--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:11</t>
+    <t xml:space="preserve">2026-10-05 10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -542,7 +542,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1312662.12</v>
+        <v>1312662.13</v>
       </c>
     </row>
     <row r="5">
@@ -593,7 +593,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1248008.62</v>
+        <v>1248008.63</v>
       </c>
     </row>
     <row r="8">
